--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/MLR.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/MLR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,1234 +466,1084 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>d_class</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 6, 8, 9, 10, 13, 18, 21, 22, 23, 31, 34, 35, 37, 38, 42]</t>
+          <t>[3, 4, 6, 7, 8, 10, 11, 14, 17, 18, 31, 32, 37, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.551984126984127</t>
+          <t>0.634065934065934</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.03954747433404249</t>
+          <t>0.06111568625318414</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.07059790442123577</t>
+          <t>0.08859306447093633</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.9261771073993449</t>
+          <t>0.8927117303594955</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.40282726287841797</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.1625902652740479</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[7, 10, 14, 17, 23, 24, 25, 26, 27, 28, 29, 32, 35, 37, 38, 39, 40, 41]</t>
+          <t>[0, 2, 7, 12, 13, 14, 15, 16, 18, 19, 26, 28, 30, 33, 34, 35, 37, 42, 43]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5736111111111111</t>
+          <t>0.42912087912087915</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.041235971327272705</t>
+          <t>0.054165508001946236</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.09449373637004302</t>
+          <t>0.12916588031757825</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.8677445791813897</t>
+          <t>0.771940373556025</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.38105010986328125</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>0.9699113368988037</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 6, 7, 8, 9, 11, 13, 16, 20, 23, 27, 34, 36, 37, 39, 40, 42]</t>
+          <t>[0, 5, 6, 7, 11, 14, 17, 18, 24, 27, 31, 33, 34, 35, 38, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7113095238095238</t>
+          <t>0.3879120879120879</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.04238311629969647</t>
+          <t>0.06657001208694649</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.07027663617771907</t>
+          <t>0.11286665218197263</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.9268474668708357</t>
+          <t>0.8258657984586533</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.4025759696960449</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.936187744140625</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 6, 9, 12, 18, 24, 26, 32, 33, 35, 37, 38, 41, 42, 43]</t>
+          <t>[2, 6, 7, 9, 11, 12, 15, 16, 19, 21, 22, 26, 27, 28, 32, 33, 37, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.448015873015873</t>
+          <t>0.6472527472527472</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04027030697018663</t>
+          <t>0.05807744503699919</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.05847960692143187</t>
+          <t>0.09514349649108926</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.9493456988711304</t>
+          <t>0.8762597448052437</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.40186285972595215</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.995387077331543</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 3, 5, 6, 8, 12, 13, 14, 15, 18, 21, 22, 28, 29, 33, 36, 37, 38, 40, 42, 43]</t>
+          <t>[1, 2, 3, 4, 8, 12, 13, 14, 19, 22, 28, 37, 38, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8115079365079365</t>
+          <t>0.3934065934065934</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.06512012385999907</t>
+          <t>0.045653965152115235</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.07754200111342084</t>
+          <t>0.11463368402720625</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.9109402549794191</t>
+          <t>0.8203706527649011</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.3992178440093994</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>0.9748361110687256</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[0, 1, 5, 6, 8, 12, 13, 15, 16, 18, 20, 26, 27, 30, 34, 36, 37, 39, 40, 41, 42, 43]</t>
+          <t>[0, 2, 6, 10, 11, 13, 14, 15, 16, 23, 24, 29, 33, 43]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7313492063492063</t>
+          <t>0.22967032967032966</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.043992257998347085</t>
+          <t>0.07493699852967332</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.05857531101994849</t>
+          <t>0.16714979849242861</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.9491797678293465</t>
+          <t>0.6180869425507769</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.377849817276001</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.9746851921081543</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 5, 8, 9, 11, 12, 17, 20, 21, 22, 24, 26, 27, 28, 32, 33, 36, 37, 38]</t>
+          <t>[3, 4, 7, 8, 12, 14, 16, 21, 22, 23, 25, 26, 28, 32, 33, 35, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.0178571428571428</t>
+          <t>0.5208791208791208</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.0496411932326524</t>
+          <t>0.051588974204385185</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07085459167169712</t>
+          <t>0.15320294558220338</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.9256393054751694</t>
+          <t>0.6791610967608082</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.3938453197479248</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.9668371677398682</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 6, 7, 9, 12, 17, 27, 32, 33, 37, 39, 41, 43]</t>
+          <t>[2, 3, 7, 8, 9, 12, 14, 16, 18, 21, 24, 26, 27, 28, 30, 31, 32, 33, 34, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5081349206349206</t>
+          <t>0.510989010989011</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.04441389512782074</t>
+          <t>0.06023171766116201</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.058948300495529314</t>
+          <t>0.06562977262110964</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.9485304921356573</t>
+          <t>0.9411217909143123</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.3772869110107422</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.9913558959960938</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[11, 17, 19, 20, 24, 26, 31, 35, 38, 39, 40]</t>
+          <t>[3, 5, 6, 9, 10, 11, 15, 18, 20, 23, 26, 30, 31, 37, 38, 42]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.15476190476190477</t>
+          <t>0.25054945054945055</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.06574712969536675</t>
+          <t>0.04956384920349398</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05801490678525159</t>
+          <t>0.06332357913636703</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.9501475351664301</t>
+          <t>0.9451869839035323</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.38062596321105957</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>0.9826815128326416</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 10, 14, 15, 16, 22, 23, 24, 27, 31, 32, 35, 37, 38, 40, 41, 42]</t>
+          <t>[0, 4, 6, 8, 10, 14, 21, 23, 24, 27, 28, 30, 34, 35, 37, 38, 40, 44]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5013888888888889</t>
+          <t>0.5291208791208791</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.04023399073532767</t>
+          <t>0.052526798150885776</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.07675187271381728</t>
+          <t>0.09533693193662188</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.912745989052982</t>
+          <t>0.8757560827775619</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.39455103874206543</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.975867748260498</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 7, 10, 11, 12, 13, 15, 16, 17, 18, 22, 24, 26, 27, 28, 31, 32, 35, 37, 38, 41]</t>
+          <t>[0, 1, 2, 5, 7, 8, 12, 16, 17, 18, 21, 22, 24, 27, 28, 29, 32, 37, 38, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.8886904761904761</t>
+          <t>0.6747252747252748</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.05062694024188966</t>
+          <t>0.05190636970818835</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.09069334707268495</t>
+          <t>0.12333926026313133</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.878168862742562</t>
+          <t>0.7920516536977543</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.379180908203125</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>0.9844167232513428</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 9, 10, 13, 14, 15, 17, 18, 20, 23, 28, 29, 30, 32, 36, 37, 38, 41, 42]</t>
+          <t>[0, 1, 4, 6, 10, 14, 20, 21, 23, 24, 29, 32, 37, 38, 44]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7130952380952381</t>
+          <t>0.15824175824175823</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.049070318604390976</t>
+          <t>0.05680416336290774</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.07877250872151695</t>
+          <t>0.08945258275223825</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.9080912642595473</t>
+          <t>0.8906198383010548</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.3722851276397705</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.9598343372344971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[1, 2, 5, 8, 11, 15, 16, 19, 22, 25, 28, 32, 34, 35, 37, 39, 41, 42]</t>
+          <t>[2, 4, 5, 8, 9, 10, 12, 13, 14, 15, 23, 27, 28, 29, 33, 37, 38, 39, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.0668650793650793</t>
+          <t>0.7538461538461538</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.0439420499997966</t>
+          <t>0.0617449563769936</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.04779146647831842</t>
+          <t>0.10216579069416055</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.9661695205823118</t>
+          <t>0.8573197724666418</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.36672234535217285</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.2907285690307617</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 9, 11, 12, 14, 16, 18, 19, 26, 32, 34, 35, 37, 39, 41, 43, 44]</t>
+          <t>[0, 3, 4, 7, 8, 10, 11, 13, 17, 18, 19, 21, 22, 28, 31, 32, 35, 37, 38, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.6456349206349206</t>
+          <t>0.871978021978022</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.05002107358432162</t>
+          <t>0.06097908640839883</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.059670372295156225</t>
+          <t>0.07766207856350653</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.9472618448846526</t>
+          <t>0.9175537680033946</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.378861665725708</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.366163730621338</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 6, 8, 11, 14, 15, 16, 19, 21, 24, 28, 31, 34, 35, 37, 39, 43, 44]</t>
+          <t>[5, 6, 8, 10, 11, 12, 15, 16, 17, 18, 21, 23, 25, 31, 32, 37, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.6178571428571429</t>
+          <t>0.6186813186813187</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.052220647387181886</t>
+          <t>0.051796685179082924</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0664892137465974</t>
+          <t>0.06449164654237939</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.9345198247768104</t>
+          <t>0.9431461705425636</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.368074893951416</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.3777999877929688</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 8, 9, 10, 20, 21, 23, 24, 32, 34, 35, 36, 37, 38, 41]</t>
+          <t>[0, 3, 6, 11, 12, 13, 14, 24, 25, 26, 27, 31, 32, 36, 37, 39, 40, 42]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.6482142857142856</t>
+          <t>0.42472527472527477</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.04661396124055027</t>
+          <t>0.05744935248476807</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.06959984534213988</t>
+          <t>0.06285581023475424</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.9282496560360786</t>
+          <t>0.9459937962938636</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.373211145401001</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.391955852508545</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[0, 3, 5, 8, 9, 10, 15, 22, 27, 28, 30, 31, 32, 35, 37, 38, 42, 43]</t>
+          <t>[1, 3, 8, 10, 11, 12, 17, 19, 20, 21, 26, 28, 29, 33, 34, 37, 38, 40, 41]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.8184523809523809</t>
+          <t>0.5137362637362638</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.045063870688888875</t>
+          <t>0.05771696542309829</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.07124636481986513</t>
+          <t>0.09121522588907512</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.9248147134963334</t>
+          <t>0.8862667451213052</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.37267565727233887</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.353506326675415</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 6, 8, 9, 11, 12, 16, 17, 18, 19, 21, 26, 27, 28, 29, 30, 31, 34, 35, 37, 40, 41, 44]</t>
+          <t>[1, 8, 10, 11, 13, 15, 16, 17, 26, 27, 30, 31, 32, 33, 34, 36, 37, 39, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.955952380952381</t>
+          <t>0.7956043956043957</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.05155874402701025</t>
+          <t>0.0510193385104899</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.07843531023240909</t>
+          <t>0.09047389877529285</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.9088764405929803</t>
+          <t>0.8881079054533948</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.3778836727142334</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2990827560424805</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 6, 7, 9, 13, 19, 21, 22, 26, 32, 33, 34, 36, 37, 41, 43]</t>
+          <t>[1, 5, 8, 9, 10, 11, 12, 13, 16, 18, 21, 22, 26, 29, 30, 32, 34, 36, 37, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.5845238095238096</t>
+          <t>0.767032967032967</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.0655551621332617</t>
+          <t>0.0529403116571618</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.061853754565342874</t>
+          <t>0.08813250706846551</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.9433317799416935</t>
+          <t>0.8938243224140646</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.3709380626678467</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.206855297088623</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 6, 7, 8, 9, 10, 16, 17, 18, 20, 21, 24, 26, 28, 33, 36, 37, 38, 41, 42]</t>
+          <t>[5, 6, 8, 10, 13, 19, 22, 23, 25, 27, 28, 29, 30, 31, 32, 34, 35, 37, 38, 39, 42]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9859126984126985</t>
+          <t>0.6368131868131868</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.04924938084887426</t>
+          <t>0.05376900554034336</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.09297897000767887</t>
+          <t>0.08182279565454688</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.8719507910026595</t>
+          <t>0.9084830747753643</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.3669877052307129</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.3758149147033691</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 7, 8, 12, 13, 14, 16, 19, 20, 32, 34, 37, 38, 39, 43]</t>
+          <t>[2, 7, 11, 12, 15, 18, 19, 23, 26, 27, 32, 33, 36, 37, 38, 42]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.6581349206349206</t>
+          <t>0.3148351648351648</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.0479347972213402</t>
+          <t>0.06397139916987211</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.06362893561130663</t>
+          <t>0.1137537098631371</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.9400323879858249</t>
+          <t>0.8231178816402935</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.3928649425506592</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.3121097087860107</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 7, 9, 10, 11, 12, 15, 16, 23, 25, 26, 27, 35, 36, 37, 39, 41, 44]</t>
+          <t>[4, 6, 8, 11, 12, 14, 15, 16, 17, 18, 21, 22, 26, 28, 29, 31, 36, 37, 38, 39, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.5884920634920634</t>
+          <t>0.695054945054945</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.05089276969114611</t>
+          <t>0.06184040763658692</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.0635447596232231</t>
+          <t>0.11514994951785035</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.9401909477356105</t>
+          <t>0.8187490481157755</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.41751956939697266</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.429553508758545</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 8, 9, 10, 13, 16, 19, 24, 26, 29, 30, 35, 36, 37, 39, 44]</t>
+          <t>[3, 4, 6, 7, 11, 12, 13, 18, 19, 20, 21, 22, 24, 28, 29, 30, 33, 36, 37, 38, 39]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.4170634920634921</t>
+          <t>0.39615384615384613</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.0417524647529607</t>
+          <t>0.04825431970833959</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.061734620390575076</t>
+          <t>0.11032211704350278</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.943549862744903</t>
+          <t>0.8336288698865464</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.38558435440063477</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4386913776397705</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[5, 6, 8, 11, 12, 14, 15, 18, 20, 26, 29, 30, 31, 34, 35, 37, 44]</t>
+          <t>[1, 2, 6, 7, 14, 20, 22, 23, 26, 27, 31, 32, 33, 35, 37, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.4027777777777778</t>
+          <t>0.18406593406593408</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.049195134226318285</t>
+          <t>0.05265013662962483</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.057214001876047096</t>
+          <t>0.08979191101917736</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.9515144763952839</t>
+          <t>0.8897884217712418</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.36542844772338867</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.2917890548706055</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 7, 8, 13, 15, 18, 22, 23, 24, 26, 27, 28, 29, 33, 35, 37, 41]</t>
+          <t>[1, 8, 9, 10, 13, 16, 18, 20, 29, 30, 35, 37, 39, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>0.3247252747252747</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.06636040959472853</t>
+          <t>0.05714789913515796</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.10614920717408545</t>
+          <t>0.10398719347494813</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.8331059138632108</t>
+          <t>0.8521870425382958</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.38489460945129395</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.2548496723175049</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[2, 5, 6, 7, 8, 9, 10, 13, 14, 16, 18, 23, 28, 29, 30, 31, 32, 34, 35, 37, 40, 41, 42]</t>
+          <t>[1, 5, 8, 9, 10, 12, 13, 14, 15, 16, 21, 23, 28, 29, 31, 36, 37]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.7428571428571428</t>
+          <t>0.28626373626373625</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.043519502054163786</t>
+          <t>0.04998322779662249</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.07369669637109223</t>
+          <t>0.07282327541272544</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.9195541808543486</t>
+          <t>0.9275074779507159</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.3960998058319092</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2760839462280273</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[5, 6, 7, 8, 9, 10, 11, 19, 20, 21, 23, 24, 26, 27, 28, 30, 34, 35, 37, 38, 40, 43]</t>
+          <t>[3, 8, 10, 12, 13, 14, 18, 20, 22, 24, 26, 27, 29, 37, 38, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.6708333333333334</t>
+          <t>0.24505494505494504</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.050204248378943564</t>
+          <t>0.049110797524946355</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.08642855235341308</t>
+          <t>0.09250582977439344</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.8893575164081701</t>
+          <t>0.8830255536111599</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.36716341972351074</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.2823011875152588</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[2, 4, 7, 8, 9, 12, 13, 14, 15, 16, 20, 25, 27, 30, 31, 37, 38, 43, 44]</t>
+          <t>[0, 1, 3, 4, 6, 13, 19, 22, 23, 24, 26, 27, 37, 38, 40, 42]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.43293650793650795</t>
+          <t>0.3274725274725274</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.05472270990206272</t>
+          <t>0.06024940831834393</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.04688328591412992</t>
+          <t>0.10582345699921952</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.9674430641878999</t>
+          <t>0.846920624496633</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.36859798431396484</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.3110930919647217</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 8, 12, 13, 14, 18, 25, 28, 29, 32, 33, 34, 35, 37, 38, 41, 42, 43, 44]</t>
+          <t>[1, 4, 7, 8, 13, 14, 17, 20, 21, 22, 23, 26, 28, 31, 33, 35, 38, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.7609126984126984</t>
+          <t>0.3879120879120879</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.06396061844398507</t>
+          <t>0.04852418776126261</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.05858401610967141</t>
+          <t>0.09399223869607944</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.9491646615483548</t>
+          <t>0.8792361973855739</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.3640873432159424</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.3813250064849854</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[0, 3, 6, 8, 12, 13, 14, 17, 20, 21, 25, 30, 34, 35, 37, 38, 39, 43]</t>
+          <t>[4, 6, 10, 11, 14, 17, 18, 20, 21, 25, 28, 32, 33, 34, 35, 37, 41, 44]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1703,123 +1553,108 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.4097222222222222</t>
+          <t>0.42472527472527477</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.04621191263693021</t>
+          <t>0.059002458998527164</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.06040152747594292</t>
+          <t>0.0769608301200798</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.9459615005138097</t>
+          <t>0.9190359397868879</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.3645470142364502</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.26491117477417</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[3, 8, 9, 10, 16, 17, 18, 24, 28, 29, 31, 34, 36, 37, 43, 44]</t>
+          <t>[0, 7, 8, 11, 12, 15, 16, 19, 20, 24, 25, 26, 27, 29, 37, 43, 44]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.3845238095238095</t>
+          <t>0.3626373626373626</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.054326866119768835</t>
+          <t>0.061996795828785346</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.061410366767289365</t>
+          <t>0.1471192196749064</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.9441413004577346</t>
+          <t>0.7041363452599226</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.3668022155761719</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.2476310729980469</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 7, 10, 13, 15, 19, 28, 30, 31, 32, 33, 37, 39, 40]</t>
+          <t>[0, 3, 5, 7, 8, 9, 11, 14, 19, 22, 24, 26, 29, 31, 33, 38, 39, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.5434523809523809</t>
+          <t>0.5417582417582417</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.04327681333374564</t>
+          <t>0.06678352911747258</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.05800484204840882</t>
+          <t>0.10209006681509303</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.9501648310113778</t>
+          <t>0.85753119932924</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.36736369132995605</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.2842659950256348</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[9, 12, 13, 14, 15, 18, 24, 29, 30, 31, 34, 39, 40, 41]</t>
+          <t>[1, 2, 4, 8, 9, 11, 13, 21, 25, 26, 35, 37, 42, 44]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1829,81 +1664,71 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.1845238095238095</t>
+          <t>0.39615384615384613</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.0699293791284065</t>
+          <t>0.04793696861389733</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.0748964831690417</t>
+          <t>0.08170017428980891</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.91691353358784</t>
+          <t>0.9087571676236335</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.36162614822387695</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.2511754035949707</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[0, 4, 6, 10, 11, 12, 13, 14, 16, 19, 20, 21, 24, 28, 30, 32, 37, 41, 44]</t>
+          <t>[0, 5, 7, 8, 9, 19, 20, 21, 24, 26, 27, 28, 29, 31, 33, 35, 36, 38, 41, 44]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.5101190476190476</t>
+          <t>0.4906593406593407</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.05690888920717667</t>
+          <t>0.05567578877422796</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.06865729905220132</t>
+          <t>0.06488917412596704</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.930179835582098</t>
+          <t>0.9424431144718597</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.36592578887939453</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2691776752471924</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 2, 5, 6, 7, 8, 13, 14, 15, 16, 22, 25, 28, 34, 35, 36, 37, 38, 40]</t>
+          <t>[0, 2, 5, 7, 8, 12, 15, 16, 18, 22, 26, 29, 30, 31, 32, 33, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1913,2181 +1738,1921 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.7035714285714285</t>
+          <t>0.24505494505494504</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.039969724359066816</t>
+          <t>0.04917509253422251</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.07686600154795158</t>
+          <t>0.1058183558775084</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.9124863054248622</t>
+          <t>0.8469353822399034</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.3665189743041992</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2741472721099854</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 7, 8, 14, 15, 27, 31, 35, 37, 42, 44]</t>
+          <t>[0, 1, 2, 3, 8, 10, 16, 18, 20, 21, 28, 30, 33, 38, 41, 44]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.39722222222222225</t>
+          <t>0.2967032967032967</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.03521364495406025</t>
+          <t>0.05681828070405923</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.055272745959605116</t>
+          <t>0.11788698895190516</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.954748860480897</t>
+          <t>0.8100302100239237</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.3669440746307373</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.2506189346313477</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 10, 13, 14, 17, 18, 21, 25, 27, 29, 30, 31, 32, 37, 39, 42]</t>
+          <t>[4, 6, 8, 21, 22, 27, 28, 31, 32, 33, 34, 36, 38, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.23531746031746031</t>
+          <t>0.5906593406593407</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.049130405715497906</t>
+          <t>0.05241398256191908</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.05297475419195825</t>
+          <t>0.09342336236533344</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.9584333199412667</t>
+          <t>0.8806935894377036</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.367354154586792</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3329598903656006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[4, 6, 7, 8, 9, 10, 13, 14, 15, 18, 19, 25, 26, 30, 32, 34, 36, 37, 38, 39, 44]</t>
+          <t>[1, 6, 7, 10, 12, 14, 24, 27, 31, 32, 34, 36, 37, 42, 44]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.6488095238095238</t>
+          <t>0.25054945054945055</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.05352369997446722</t>
+          <t>0.050998537105070296</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.07908723311521511</t>
+          <t>0.054518054741355106</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.9073553804769713</t>
+          <t>0.9593712468057805</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.3679184913635254</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2932507991790771</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[0, 3, 7, 8, 9, 12, 18, 19, 25, 29, 35, 36, 37, 38, 41, 43, 44]</t>
+          <t>[0, 1, 3, 8, 10, 15, 18, 20, 23, 27, 31, 32, 34, 35, 37, 39]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.5890873015873016</t>
+          <t>0.37637362637362637</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.046603787396596943</t>
+          <t>0.05927399035262622</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.05917503666785803</t>
+          <t>0.06153138165043873</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.9481337905312166</t>
+          <t>0.9482457372577234</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.36624574661254883</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.2610509395599365</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 10, 12, 14, 20, 23, 24, 25, 26, 30, 34, 35, 37, 38, 39, 41, 44]</t>
+          <t>[3, 4, 8, 9, 10, 11, 12, 13, 15, 19, 20, 26, 27, 28, 29, 30, 31, 32, 34, 35, 37, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.37083333333333335</t>
+          <t>1.004945054945055</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.045181886439086084</t>
+          <t>0.0456583908232629</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.06951941582912867</t>
+          <t>0.1046477221175363</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.9284153894742353</t>
+          <t>0.8503032570914075</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.366391658782959</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2776908874511719</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 13, 18, 20, 23, 28, 31, 34, 39, 40, 42]</t>
+          <t>[5, 6, 9, 12, 13, 14, 16, 18, 20, 21, 23, 25, 26, 29, 32, 34, 37, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2220238095238095</t>
+          <t>0.3576923076923077</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.06136410757763703</t>
+          <t>0.04971446067965356</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.08142193327507288</t>
+          <t>0.10513367357224447</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.9018048001697562</t>
+          <t>0.8489097388783127</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.36498069763183594</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.2930405139923096</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[1, 6, 9, 10, 11, 12, 13, 15, 18, 22, 23, 28, 29, 32, 34, 35, 36, 37, 38, 42, 43]</t>
+          <t>[0, 1, 2, 9, 11, 19, 24, 25, 30, 35, 37, 38, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.6746031746031745</t>
+          <t>0.43131868131868134</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.05897653263581722</t>
+          <t>0.059454633171639</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.08776061105540743</t>
+          <t>0.08809782133321631</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.885920734799764</t>
+          <t>0.8939078797043541</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.3663308620452881</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.3106613159179688</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[0, 8, 9, 17, 22, 25, 26, 29, 34, 37, 39, 40, 42, 44]</t>
+          <t>[0, 3, 5, 6, 7, 8, 9, 10, 12, 13, 15, 16, 21, 26, 32, 37, 38, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.1121031746031746</t>
+          <t>0.578021978021978</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.05089837784720648</t>
+          <t>0.05641859849270629</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0322171125059842</t>
+          <t>0.07183630070036404</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.9846262198700378</t>
+          <t>0.9294591462411529</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.3669431209564209</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.403167963027954</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 14, 21, 23, 25, 27, 28, 30, 31, 34, 35, 37, 40, 42]</t>
+          <t>[3, 7, 9, 11, 15, 24, 25, 31, 32, 33, 34, 35, 38, 39, 41]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.46865079365079365</t>
+          <t>0.36813186813186816</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.05270677114319593</t>
+          <t>0.0568630086477833</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.06297895128205999</t>
+          <t>0.10033029823345467</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.9412512964275381</t>
+          <t>0.8624004547415192</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.36514878273010254</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.3817625045776367</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 9, 10, 14, 16, 18, 19, 23, 29, 31, 35, 37, 38, 39]</t>
+          <t>[1, 4, 5, 6, 9, 11, 12, 16, 21, 22, 23, 28, 29, 30, 33, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.37083333333333335</t>
+          <t>0.378021978021978</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.06019395032241248</t>
+          <t>0.0775384265470356</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.06010106853648878</t>
+          <t>0.10558129838441349</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.9464977772669607</t>
+          <t>0.8476204140712829</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.36696505546569824</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.447463035583496</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 6, 7, 12, 14, 18, 25, 28, 32, 35, 36, 37, 38, 44]</t>
+          <t>[1, 3, 6, 9, 10, 17, 18, 19, 20, 23, 26, 29, 30, 35, 37, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.4386904761904762</t>
+          <t>0.29945054945054944</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.05511491581537995</t>
+          <t>0.05189900479118442</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.07497955051963201</t>
+          <t>0.09216158757677256</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.9167291297358838</t>
+          <t>0.8838945283932695</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.3627469539642334</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.361396074295044</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[2, 5, 6, 9, 10, 12, 14, 16, 17, 18, 26, 27, 29, 31, 34, 35, 37, 38, 41, 43]</t>
+          <t>[6, 7, 12, 19, 22, 25, 26, 28, 29, 30, 32, 33, 34, 36, 37, 38, 43]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.38749999999999996</t>
+          <t>0.3351648351648352</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.04701130048604938</t>
+          <t>0.05826806081523017</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.06449180504830213</t>
+          <t>0.07458446557956533</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.938394923214277</t>
+          <t>0.9239586958417751</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.36542487144470215</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.4109535217285156</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[0, 6, 7, 8, 12, 13, 14, 18, 19, 20, 24, 25, 26, 31, 32, 33, 37, 38, 39, 42]</t>
+          <t>[0, 1, 4, 5, 6, 8, 10, 14, 15, 16, 17, 20, 24, 25, 26, 27, 28, 29, 30, 39, 44]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.6738095238095239</t>
+          <t>0.6186813186813187</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.05308969852015312</t>
+          <t>0.050115728376321146</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.052507397817810074</t>
+          <t>0.16228004443689867</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.9591635077708613</t>
+          <t>0.6400161410830633</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.3658769130706787</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3184213638305664</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[2, 3, 9, 10, 11, 12, 23, 24, 26, 28, 30, 35, 37, 43, 44]</t>
+          <t>[3, 4, 7, 8, 9, 12, 13, 15, 16, 26, 28, 29, 30, 31, 32, 35, 37, 38, 42, 43]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.43134920634920637</t>
+          <t>0.482967032967033</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.039305293355230905</t>
+          <t>0.0467021489940815</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.06386031327236041</t>
+          <t>0.12593920839338438</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.9395954674805165</t>
+          <t>0.7831922958501537</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.36581873893737793</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3982539176940918</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 8, 11, 12, 18, 19, 20, 25, 26, 31, 37, 38, 39, 40, 41, 42, 44]</t>
+          <t>[2, 3, 5, 8, 13, 16, 20, 21, 23, 28, 29, 33, 35, 38, 41, 44]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.7944444444444445</t>
+          <t>0.15824175824175823</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.06286369121512017</t>
+          <t>0.049784653754462685</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.027283296826457762</t>
+          <t>0.13549790041004903</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.988974427887992</t>
+          <t>0.749032246212781</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.36963725090026855</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.3619444370269775</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[0, 4, 5, 6, 8, 9, 10, 18, 20, 24, 26, 30, 32, 35, 37, 39, 40, 41, 43, 44]</t>
+          <t>[4, 5, 6, 7, 8, 11, 21, 22, 23, 26, 27, 31, 34, 35, 37, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.4646825396825397</t>
+          <t>0.47307692307692306</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.044188974487461834</t>
+          <t>0.05532832831203518</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.06169853830959229</t>
+          <t>0.11753025612192032</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.9436158303713268</t>
+          <t>0.811178189555088</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.3671081066131592</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3926384449005127</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[5, 7, 10, 11, 12, 14, 15, 18, 19, 21, 25, 27, 30, 32, 37, 39]</t>
+          <t>[0, 2, 5, 6, 7, 10, 15, 21, 23, 25, 29, 33, 34, 37, 38, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.44265873015873014</t>
+          <t>0.40604395604395604</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.0444930237671481</t>
+          <t>0.052591418734860715</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.05217328438623902</t>
+          <t>0.08430024692907662</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.9596815532850105</t>
+          <t>0.9028572294111102</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.3671102523803711</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3742938041687012</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[0, 1, 5, 8, 9, 14, 18, 20, 21, 35, 36, 37, 39, 40, 41, 44]</t>
+          <t>[6, 11, 12, 15, 18, 23, 24, 26, 27, 29, 31, 33, 38, 39, 40]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.6515873015873016</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.04701967676631653</t>
+          <t>0.06842315237583343</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.06897980755013826</t>
+          <t>0.0723000258963175</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.9295223531770131</t>
+          <t>0.92854548135338</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.36603641510009766</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.363487720489502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 6, 7, 8, 13, 21, 23, 24, 25, 26, 31, 32, 34, 36, 37, 38, 39, 41, 42]</t>
+          <t>[5, 8, 11, 18, 22, 23, 25, 26, 28, 29, 32, 34, 36, 37, 38, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.7154761904761905</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.04931301301936517</t>
+          <t>0.054543286558464896</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.07687046554995983</t>
+          <t>0.1302168345116792</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9124761403936569</t>
+          <t>0.7682140753156461</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.365070104598999</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.379138469696045</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 5, 10, 11, 17, 18, 25, 28, 35, 37, 43]</t>
+          <t>[1, 6, 8, 9, 10, 13, 14, 17, 18, 21, 22, 25, 27, 29, 30, 32, 33, 34, 38, 39, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.2724206349206349</t>
+          <t>0.5318681318681319</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.04945548342726137</t>
+          <t>0.0659238228589971</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0714721633328128</t>
+          <t>0.09048975391938695</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9243373943294948</t>
+          <t>0.8880686848438151</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.36831068992614746</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.3361172676086426</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[2, 3, 10, 15, 16, 17, 18, 20, 21, 23, 26, 27, 28, 33, 35, 37, 38, 39, 41, 42, 43]</t>
+          <t>[1, 6, 9, 11, 15, 16, 21, 30, 32, 37, 38, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.6361111111111111</t>
+          <t>0.22527472527472528</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.05163416155156429</t>
+          <t>0.053913825963680974</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.09543363390920313</t>
+          <t>0.115601830713971</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.865100493612456</t>
+          <t>0.8173236961397166</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.3667147159576416</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.3246870040893555</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[1, 4, 7, 9, 10, 12, 15, 16, 23, 28, 29, 32, 33, 34, 35, 37, 39, 44]</t>
+          <t>[2, 3, 6, 7, 12, 18, 21, 23, 25, 26, 28, 30, 34, 37]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.44047619047619047</t>
+          <t>0.17857142857142858</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.053808857103240314</t>
+          <t>0.04831626325176043</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.056838213113483874</t>
+          <t>0.07877525463265217</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.9521493027546295</t>
+          <t>0.9151733290002401</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.37065911293029785</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.330507755279541</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 7, 9, 10, 11, 12, 16, 17, 20, 23, 26, 27, 34, 35, 37, 38, 42, 43, 44]</t>
+          <t>[1, 8, 10, 13, 16, 18, 21, 22, 24, 28, 29, 33, 35, 37, 38, 39, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.589484126984127</t>
+          <t>0.5675824175824176</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.05885019397208565</t>
+          <t>0.04018107820213982</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.05304800418807432</t>
+          <t>0.1543674705791599</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9583182891404484</t>
+          <t>0.6742650431141755</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.36728978157043457</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.4396014213562012</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 7, 11, 13, 17, 18, 20, 24, 29, 31, 33, 34, 37, 38]</t>
+          <t>[2, 3, 5, 6, 7, 11, 13, 22, 24, 25, 27, 29, 30, 32, 34, 37, 39, 40]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.3515873015873016</t>
+          <t>0.3576923076923077</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.06181042485215443</t>
+          <t>0.06155319349058648</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.05416916347580584</t>
+          <t>0.12057824343047852</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.956537800990388</t>
+          <t>0.8012575231796075</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.36707258224487305</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.2535507678985596</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[0, 7, 8, 9, 10, 12, 17, 23, 27, 30, 31, 32, 37, 38, 40, 42, 43]</t>
+          <t>[2, 4, 6, 8, 10, 11, 12, 14, 15, 18, 21, 23, 24, 25, 28, 31, 32, 33, 38, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.3831349206349206</t>
+          <t>0.6802197802197802</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.0580397925625518</t>
+          <t>0.05330481449507744</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.05204825786941286</t>
+          <t>0.09400399499207678</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.9598745576210019</t>
+          <t>0.8792059858741277</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.3701941967010498</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.4457998275756836</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[0, 1, 6, 7, 8, 9, 11, 12, 16, 18, 19, 21, 24, 26, 30, 31, 34, 37, 38, 40]</t>
+          <t>[0, 5, 10, 14, 18, 19, 23, 24, 27, 28, 33, 34, 36, 37, 38, 39, 44]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.5367063492063492</t>
+          <t>0.5648351648351648</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.04126061211081869</t>
+          <t>0.06293660666182141</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.04788926780286925</t>
+          <t>0.10769061976269562</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.9660309162917106</t>
+          <t>0.8414710639406898</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.3683183193206787</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.2604775428771973</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[4, 9, 10, 13, 14, 17, 18, 24, 31, 33, 34, 37, 38, 43]</t>
+          <t>[1, 3, 4, 6, 7, 11, 12, 13, 15, 18, 21, 23, 25, 29, 35, 37, 38, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.25436507936507935</t>
+          <t>0.5445054945054946</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.04943155595390017</t>
+          <t>0.06376754714842417</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.07126700753934068</t>
+          <t>0.09087122926315287</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.924771139241784</t>
+          <t>0.8871229636390686</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.365480899810791</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2427079677581787</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[7, 8, 9, 11, 12, 13, 21, 22, 24, 25, 31, 34, 36, 37, 38, 39, 41, 42, 43, 44]</t>
+          <t>[2, 8, 10, 12, 15, 18, 21, 23, 24, 26, 27, 28, 30, 31, 33, 40, 44]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0.7494047619047619</t>
+          <t>0.21978021978021978</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.05308994817192497</t>
+          <t>0.05103401724811413</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.07465758612305558</t>
+          <t>0.06335077268071154</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.9174427294653704</t>
+          <t>0.9451398962229014</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.36449432373046875</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.256202220916748</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[1, 2, 5, 7, 8, 9, 11, 12, 16, 17, 21, 24, 26, 27, 28, 29, 31, 36, 37, 38, 41, 42, 43]</t>
+          <t>[3, 6, 7, 9, 11, 13, 16, 18, 25, 26, 27, 29, 33, 34, 37, 40, 41]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0.9781746031746031</t>
+          <t>0.38076923076923075</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.04981545081454615</t>
+          <t>0.06098327033790561</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.06351426527653707</t>
+          <t>0.13266733559706975</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.9402483372156194</t>
+          <t>0.7594082082142893</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.37140917778015137</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.3774340152740479</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[2, 4, 10, 12, 15, 16, 20, 21, 22, 23, 24, 26, 29, 31, 32, 39, 43, 44]</t>
+          <t>[1, 2, 4, 7, 8, 9, 15, 17, 25, 26, 31, 33, 41, 43]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0.18035714285714285</t>
+          <t>0.22967032967032966</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.07051493995816843</t>
+          <t>0.05666832065122425</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.05219006611735901</t>
+          <t>0.09630166393568738</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.959655611956704</t>
+          <t>0.8732288662320342</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.36415767669677734</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.458885908126831</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[1, 4, 8, 11, 12, 21, 23, 25, 26, 28, 32, 34, 35, 37, 38, 44]</t>
+          <t>[0, 1, 2, 5, 6, 9, 10, 13, 14, 15, 23, 25, 27, 29, 35, 37, 39, 40, 42]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.6811507936507937</t>
+          <t>0.6313186813186813</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.039445462248141515</t>
+          <t>0.06237197623105435</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.04573828864058267</t>
+          <t>0.0888029977122842</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.9690138756095946</t>
+          <t>0.8922026598034937</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.36554479598999023</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4141991138458252</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[0, 4, 8, 9, 10, 11, 13, 23, 24, 27, 28, 29, 31, 33, 34, 35, 37, 39, 41]</t>
+          <t>[1, 7, 8, 9, 12, 13, 14, 15, 18, 25, 29, 30, 32, 37, 40, 44]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.751984126984127</t>
+          <t>0.22967032967032966</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.048083359992939514</t>
+          <t>0.04909221667518275</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.057863449628017136</t>
+          <t>0.09646436194993066</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.9504074909989777</t>
+          <t>0.8728001543321606</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.3678596019744873</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4292781352996826</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[3, 6, 8, 10, 12, 13, 14, 15, 18, 22, 23, 24, 29, 31, 32, 36, 37, 42]</t>
+          <t>[3, 4, 10, 12, 15, 16, 18, 22, 23, 24, 25, 28, 29, 37, 39, 40, 43]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.5041666666666667</t>
+          <t>0.22967032967032966</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.03672882497020681</t>
+          <t>0.05867875574636493</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.06860136063994964</t>
+          <t>0.13107189057302804</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.930293560943928</t>
+          <t>0.7651600822119042</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.366192102432251</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.409944772720337</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 7, 8, 9, 11, 15, 20, 23, 24, 31, 36, 37, 42, 44]</t>
+          <t>[2, 5, 8, 9, 10, 12, 16, 20, 22, 23, 25, 29, 32, 33, 37, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0.5083333333333333</t>
+          <t>0.41648351648351645</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.0446261787755631</t>
+          <t>0.060696845974094596</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.06975399540909599</t>
+          <t>0.16446698149852607</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.927931478071842</t>
+          <t>0.6302482519849666</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.36401891708374023</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.4441673755645752</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[1, 2, 6, 8, 10, 13, 14, 18, 23, 24, 27, 28, 30, 33, 34, 36, 37, 38, 39]</t>
+          <t>[1, 2, 8, 11, 12, 13, 14, 19, 20, 21, 26, 28, 30, 32, 35, 37, 38, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.7251984126984127</t>
+          <t>0.5346153846153846</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.047967466483011346</t>
+          <t>0.056474210308723884</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.07933095564347578</t>
+          <t>0.19510420199087905</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.9067834962000536</t>
+          <t>0.4796614071268721</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.36680006980895996</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.401125431060791</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 8, 10, 11, 12, 19, 23, 28, 29, 30, 36, 37, 39, 41]</t>
+          <t>[3, 6, 10, 11, 17, 18, 20, 23, 24, 33, 37, 38, 42, 44]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.5847222222222221</t>
+          <t>0.12527472527472527</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.045015784350766044</t>
+          <t>0.05304036279198047</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.05981434183260373</t>
+          <t>0.08740864177752766</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.9470070501808696</t>
+          <t>0.8955612810707325</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.3637268543243408</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.5299177169799805</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 10, 12, 13, 15, 16, 17, 21, 24, 30, 31, 37, 42]</t>
+          <t>[0, 5, 8, 10, 12, 14, 18, 20, 21, 22, 24, 25, 26, 28, 29, 30, 31, 32, 39, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.1630952380952381</t>
+          <t>0.6846153846153846</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.03975614265202421</t>
+          <t>0.0523694425867834</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.04413726671568131</t>
+          <t>0.09598719647962715</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.9711451840485696</t>
+          <t>0.8740554419162102</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.36487674713134766</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4548630714416504</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 11, 13, 14, 15, 17, 26, 28, 32, 33, 35, 37, 39, 40, 43]</t>
+          <t>[0, 1, 3, 4, 7, 8, 10, 13, 17, 18, 19, 20, 21, 22, 29, 31, 32, 33, 37, 41, 44]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.8990079365079365</t>
+          <t>0.45274725274725275</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.04802778124626938</t>
+          <t>0.07140572517666352</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.07442110329501603</t>
+          <t>0.20959583894705455</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.9179649123280008</t>
+          <t>0.3994929572673581</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.3648531436920166</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.501622200012207</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 7, 10, 12, 15, 19, 24, 25, 26, 28, 30, 31, 32, 34, 37, 39]</t>
+          <t>[1, 5, 6, 8, 9, 12, 13, 20, 21, 29, 31, 32, 33, 35, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.6450396825396826</t>
+          <t>0.389010989010989</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.04724429826691912</t>
+          <t>0.051485806989244466</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.04407689771964188</t>
+          <t>0.09505787769912019</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.9712240627435063</t>
+          <t>0.8764823501248665</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.3644728660583496</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.456937313079834</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[2, 3, 12, 14, 16, 18, 22, 24, 27, 29, 35, 37, 39, 41]</t>
+          <t>[0, 1, 3, 4, 6, 8, 13, 14, 18, 19, 21, 22, 23, 24, 26, 29, 30, 31, 32, 33, 37, 38, 39, 40, 41]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.9384615384615385</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.04418724678713377</t>
+          <t>0.05679107495618212</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.06302117061491662</t>
+          <t>0.1541239430520984</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.9411725030404491</t>
+          <t>0.675291980421616</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.36230897903442383</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4063053131103516</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[0, 1, 6, 8, 9, 11, 12, 13, 14, 16, 18, 25, 26, 27, 28, 32, 34, 35, 37, 38, 41]</t>
+          <t>[1, 4, 8, 9, 10, 15, 16, 17, 18, 20, 23, 24, 27, 29, 30, 32, 35, 36, 37, 44]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.057936507936508</t>
+          <t>0.27362637362637365</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.03264774106899671</t>
+          <t>0.05849265414013042</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.052014352163663784</t>
+          <t>0.07185485376487</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.9599268182871606</t>
+          <t>0.929422704553545</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.36618852615356445</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3082528114318848</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[8, 9, 14, 15, 16, 17, 21, 23, 24, 36, 37, 38, 41, 42, 43]</t>
+          <t>[0, 2, 6, 10, 12, 13, 14, 16, 18, 20, 25, 27, 28, 34, 37, 39, 42]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.348015873015873</t>
+          <t>0.3576923076923077</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.055598748301521686</t>
+          <t>0.05944830092576817</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.06278743655196176</t>
+          <t>0.08528682863120325</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0.9416080548284507</t>
+          <t>0.9005701639264776</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.3663904666900635</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.4859864711761475</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[1, 6, 7, 11, 12, 13, 14, 16, 19, 21, 24, 25, 29, 31, 33, 37, 38, 42]</t>
+          <t>[0, 2, 3, 5, 6, 7, 8, 9, 11, 14, 16, 22, 24, 26, 27, 28, 31, 32, 34, 37, 41, 42]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.4170634920634921</t>
+          <t>1.0335164835164834</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.05095328195397604</t>
+          <t>0.06623342212135545</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.05194708518804747</t>
+          <t>0.08492032826672628</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.9600303996487188</t>
+          <t>0.9014228811213569</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.36511969566345215</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3214950561523438</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[2, 4, 6, 7, 10, 19, 20, 21, 24, 27, 34, 37, 39]</t>
+          <t>[3, 4, 7, 8, 9, 11, 13, 14, 15, 16, 19, 21, 24, 27, 28, 30, 31, 36, 37, 39, 41, 43]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.12738095238095237</t>
+          <t>0.8741758241758242</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.05151153071650285</t>
+          <t>0.05297219547059336</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.07374324048579049</t>
+          <t>0.23531317340050542</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.9194525355434426</t>
+          <t>0.24308820370342776</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.36946868896484375</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.3027453422546387</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 7, 9, 11, 12, 14, 17, 20, 21, 34, 35, 36, 37, 40, 41, 44]</t>
+          <t>[1, 5, 6, 8, 11, 13, 17, 18, 19, 21, 24, 30, 33, 37, 39, 40, 42]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.6009920634920635</t>
+          <t>0.6571428571428571</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.041139939994973805</t>
+          <t>0.051148125942354086</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.0745927645258231</t>
+          <t>0.11156924650852551</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.9175860282564052</t>
+          <t>0.8298461452208677</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.3687903881072998</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2760040760040283</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 7, 8, 10, 11, 12, 13, 14, 15, 22, 24, 25, 30, 31, 32, 36, 37, 38, 39, 40, 41, 43]</t>
+          <t>[4, 6, 9, 14, 16, 18, 23, 24, 25, 26, 27, 29, 34, 37, 38, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.1091269841269842</t>
+          <t>0.48516483516483516</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.04616855949577458</t>
+          <t>0.05306434153425632</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.0780699693671373</t>
+          <t>0.08995270386876468</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.9097233455679035</t>
+          <t>0.8893933505344147</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.3642110824584961</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.382709264755249</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[5, 8, 9, 10, 12, 13, 14, 15, 18, 24, 28, 29, 30, 32, 35, 37, 38, 40, 41, 42, 44]</t>
+          <t>[0, 2, 6, 16, 18, 19, 20, 23, 26, 30, 34, 37, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.6339285714285714</t>
+          <t>0.17857142857142858</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.06770943953347938</t>
+          <t>0.05398559712860838</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.05692230342633825</t>
+          <t>0.1274045906720771</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.9520076108748933</t>
+          <t>0.7781175533987611</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.37046027183532715</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.4620461463928223</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[0, 2, 6, 8, 12, 14, 18, 19, 22, 24, 30, 35, 37, 39, 41, 44]</t>
+          <t>[1, 3, 5, 7, 8, 12, 18, 21, 22, 23, 24, 25, 27, 28, 30, 35, 37, 38, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.5436507936507937</t>
+          <t>0.5291208791208791</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.04194948409822178</t>
+          <t>0.057693748874684495</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.06449961962661292</t>
+          <t>0.1281043208338393</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.9383799927323774</t>
+          <t>0.7756736195942526</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.3682830333709717</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.5360848903656006</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 7, 8, 9, 11, 16, 19, 21, 22, 24, 26, 27, 28, 29, 32, 34, 35, 36, 37, 39, 40, 42, 43]</t>
+          <t>[1, 2, 4, 6, 7, 15, 18, 21, 22, 24, 26, 30, 33, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.2498015873015873</t>
+          <t>0.30659340659340656</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.062425660386911205</t>
+          <t>0.0521100295079282</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.09910548793991149</t>
+          <t>0.13776678310083884</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.8545201493858884</t>
+          <t>0.7405570777087814</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.3705720901489258</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1.535654067993164</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[5, 7, 10, 11, 12, 14, 18, 19, 23, 24, 31, 32, 33, 34, 35, 37, 39, 42, 43]</t>
+          <t>[5, 9, 11, 13, 15, 16, 19, 23, 24, 29, 31, 34, 36, 38, 39, 44]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.5922619047619048</t>
+          <t>0.19395604395604396</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.046012948058802336</t>
+          <t>0.06710553160901514</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.06307904517845023</t>
+          <t>0.062420071434298036</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.9410644066986511</t>
+          <t>0.9467399812580688</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.36617279052734375</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4835426807403564</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[3, 5, 8, 11, 20, 22, 26, 29, 30, 37, 38, 40]</t>
+          <t>[0, 1, 2, 3, 5, 7, 8, 11, 15, 16, 18, 20, 25, 27, 28, 35, 37, 41]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.32539682539682535</t>
+          <t>0.682967032967033</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.04456947158478146</t>
+          <t>0.054804268439740164</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.0597055587550985</t>
+          <t>0.10083381725679016</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.9471996292142291</t>
+          <t>0.8610158711280926</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.3647420406341553</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.947045087814331</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 9, 10, 12, 13, 14, 15, 16, 22, 25, 30, 37, 38, 40, 41]</t>
+          <t>[4, 5, 6, 7, 12, 14, 15, 17, 18, 24, 26, 28, 29, 30, 34, 35, 37, 38]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4097,375 +3662,330 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.5452380952380952</t>
+          <t>0.2478021978021978</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.05418506305724215</t>
+          <t>0.053523119726749425</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.06403562646993985</t>
+          <t>0.07281927429938076</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.9392633598863084</t>
+          <t>0.9275154436135515</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.3688642978668213</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.9243390560150146</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[2, 3, 6, 12, 13, 17, 20, 22, 26, 27, 36, 37]</t>
+          <t>[2, 4, 10, 12, 13, 14, 16, 18, 19, 23, 26, 29, 31, 36, 39]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0.2376984126984127</t>
+          <t>0.17362637362637362</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.050615236328614324</t>
+          <t>0.05895681500496934</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.06458445571354639</t>
+          <t>0.07270333371955072</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.9382177890404995</t>
+          <t>0.9277460751698775</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.36608052253723145</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.9421820640563965</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 9, 24, 27, 28, 29, 32, 34, 37, 42, 43]</t>
+          <t>[0, 3, 5, 8, 15, 16, 18, 22, 23, 24, 28, 31, 33, 35, 37, 38, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0.3099206349206349</t>
+          <t>0.5620879120879121</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.04652331260228074</t>
+          <t>0.0610377046954362</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.052726392527457644</t>
+          <t>0.08007789829590094</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.9588221606256973</t>
+          <t>0.9123447112484824</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.3646090030670166</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.9380800724029541</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[3, 5, 7, 11, 12, 14, 15, 18, 21, 23, 24, 29, 30, 31, 34, 35, 37, 38, 39]</t>
+          <t>[0, 1, 5, 7, 14, 18, 19, 20, 22, 26, 27, 30, 33, 34, 35, 37, 40, 44]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.2924603174603175</t>
+          <t>0.3423076923076923</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.0388701559091852</t>
+          <t>0.06822646413652295</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.06246750409160556</t>
+          <t>0.3017588104197375</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.9422016093389373</t>
+          <t>-0.24472298777582346</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0.36141514778137207</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.9509718418121338</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 6, 7, 9, 11, 12, 14, 17, 18, 20, 24, 26, 31, 32, 34, 37, 42]</t>
+          <t>[1, 2, 8, 9, 11, 12, 13, 14, 15, 16, 19, 20, 24, 26, 27, 30, 32, 34, 37, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0.5152777777777777</t>
+          <t>0.639010989010989</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.05067048194539849</t>
+          <t>0.0616631043551916</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.04919782954010411</t>
+          <t>0.10249363981519419</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.9641491608853059</t>
+          <t>0.8564025840163855</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.36844849586486816</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.9585981369018555</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[0, 3, 5, 6, 7, 10, 15, 16, 18, 19, 21, 23, 29, 31, 37, 40]</t>
+          <t>[2, 3, 4, 6, 8, 10, 11, 12, 14, 15, 19, 21, 27, 30, 32, 34, 36, 37, 41, 43]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0.1464285714285714</t>
+          <t>0.7516483516483516</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.0484214466791988</t>
+          <t>0.0630695260923786</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.04791992605772297</t>
+          <t>0.26681233234185275</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.9659874089995351</t>
+          <t>0.026884050537646864</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.36806392669677734</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>0.960935115814209</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 8, 9, 10, 11, 13, 20, 22, 23, 27, 31, 32, 33, 36, 37, 38, 40, 42]</t>
+          <t>[2, 5, 10, 14, 16, 19, 21, 23, 27, 29, 30, 32, 37, 42]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0.8498015873015873</t>
+          <t>0.24505494505494504</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.058954719233245266</t>
+          <t>0.056235695727500555</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.07262069528671787</t>
+          <t>0.06974192272850531</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.921886114012578</t>
+          <t>0.9335124048336074</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.37263011932373047</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.9211986064910889</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 5, 8, 10, 11, 12, 14, 21, 23, 24, 25, 32, 35, 37, 38, 40, 43]</t>
+          <t>[1, 2, 3, 4, 6, 8, 10, 15, 20, 21, 23, 28, 29, 30, 32, 34, 36, 37]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0.705952380952381</t>
+          <t>0.46593406593406594</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.045689108409618415</t>
+          <t>0.05985835812254018</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.07384164389483691</t>
+          <t>0.0815202133251345</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.9192374261073132</t>
+          <t>0.9091586860768666</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.36145806312561035</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.9351487159729004</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 6, 8, 9, 12, 14, 15, 18, 19, 20, 22, 23, 30, 31, 34, 36, 37, 38, 39, 40, 41, 42, 43]</t>
+          <t>[0, 2, 3, 5, 6, 8, 9, 10, 12, 19, 21, 29, 32, 33, 35, 39, 40, 44]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.0789682539682541</t>
+          <t>0.389010989010989</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.053560820511328454</t>
+          <t>0.05204210611172999</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0.06761792396376802</t>
+          <t>0.10217665439474401</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0.9322777928748125</t>
+          <t>0.857289427325253</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0.3702843189239502</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>0.982187032699585</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[2, 8, 10, 11, 12, 14, 15, 16, 17, 18, 20, 23, 24, 28, 30, 32, 34, 35, 37, 39]</t>
+          <t>[2, 3, 5, 6, 8, 11, 12, 13, 19, 27, 31, 34, 35, 36, 37, 38, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4475,200 +3995,175 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.47579365079365077</t>
+          <t>0.6571428571428571</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.03926322344753565</t>
+          <t>0.05346439911575015</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.05017781594762278</t>
+          <t>0.09987447618213398</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.9627066886823006</t>
+          <t>0.8636479030361983</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.3638758659362793</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.3541815280914307</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[1, 6, 7, 8, 9, 10, 12, 14, 15, 16, 23, 24, 27, 29, 30, 31, 34, 37, 39]</t>
+          <t>[5, 6, 8, 10, 14, 15, 18, 21, 23, 27, 29, 31, 33, 35, 37, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.44305555555555554</t>
+          <t>0.4346153846153846</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.04961377921690087</t>
+          <t>0.05657049231059692</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.052681903485238595</t>
+          <t>0.07222031743504463</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.9588916207069751</t>
+          <t>0.9287029471382744</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.3642435073852539</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>1.4865317344665527</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 7, 9, 11, 16, 21, 25, 26, 27, 29, 30, 32, 37, 39, 42, 43]</t>
+          <t>[8, 13, 15, 16, 20, 21, 24, 25, 26, 27, 29, 37, 38, 39, 40, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0.48432539682539677</t>
+          <t>0.30659340659340656</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.05895629543345745</t>
+          <t>0.04645500532753087</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.052578006409473854</t>
+          <t>0.16521096539800298</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.9590536053176629</t>
+          <t>0.6268954629596142</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.36628031730651855</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>1.2976837158203125</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 7, 9, 10, 12, 13, 14, 16, 19, 22, 29, 34, 35, 36, 37, 41, 44]</t>
+          <t>[2, 5, 6, 7, 8, 9, 13, 17, 20, 21, 22, 23, 24, 26, 28, 31, 33, 37, 38, 39, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0.5996031746031746</t>
+          <t>0.6571428571428571</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.03906305936486507</t>
+          <t>0.0640575159325413</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.07195433718279015</t>
+          <t>0.12472454422969691</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.923313062910967</t>
+          <t>0.7873542812079946</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>0.3689730167388916</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.4027886390686035</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[2, 3, 4, 7, 8, 10, 12, 14, 17, 18, 20, 21, 23, 24, 26, 30, 32, 37, 38, 39, 40, 41, 42]</t>
+          <t>[3, 4, 6, 8, 10, 12, 15, 23, 29, 30, 37, 44]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0.6390873015873015</t>
+          <t>0.1637362637362637</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.05460860994831527</t>
+          <t>0.0483734916525634</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.07171922117251925</t>
+          <t>0.06832933254001454</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.9238134043689978</t>
+          <t>0.9361784791485825</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0.3688392639160156</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>1.2773597240447998</t>
         </is>
       </c>
     </row>
